--- a/backend/data/IND5003_Supervised.xlsx
+++ b/backend/data/IND5003_Supervised.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B846162-F901-D247-84D8-D470BC5856C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF5A758-7780-D241-A7D4-B4F81DF64A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
-  <si>
-    <t>Context ID</t>
-  </si>
   <si>
     <t>Context Text</t>
   </si>
@@ -351,6 +348,34 @@
 3. 0.987</t>
   </si>
   <si>
+    <t>venv_paths.csv, winequality-white.csv, winequality-red.csv</t>
+  </si>
+  <si>
+    <t>Supervised Learning, Data Manipulation</t>
+  </si>
+  <si>
+    <t>Data Manipulation, Basic Concepts in Statistics</t>
+  </si>
+  <si>
+    <t>Model Validation, Supervised Learning, Data Manipulation</t>
+  </si>
+  <si>
+    <t>Supervised Learning,Regression</t>
+  </si>
+  <si>
+    <t>Supervised Learning, Decision Tree, Model Validation</t>
+  </si>
+  <si>
+    <t>Consider a new wine with the following features, but unknown `type`. 
+```{python, echo=FALSE}
+wine2.sample(n=1, random_state=22).iloc[:, 0:11].T
+```
+Apply the decision tree rules to the above features to estimate the probability that the wine is *red*.</t>
+  </si>
+  <si>
+    <t>Supervised Learning, Decision Trees, Model Validation, Basic Concepts in Statistics</t>
+  </si>
+  <si>
     <t>```{r echo=FALSE}
 library(reticulate)
 tmp_out &lt;- include_supplement("venv_paths.csv")
@@ -377,8 +402,6 @@
 wine2 = pd.concat([wine_red, wine_white], ignore_index=True)
 wine2.columns = col_names
 ```
-Question
-========
 The (red and white) wine quality datasets from the unsupervised learning topic 
 have been merged into a single dataframe with 6497 rows. A decision tree 
 classifier has been fit to the dataset as follows:
@@ -393,32 +416,7 @@
 ```</t>
   </si>
   <si>
-    <t>venv_paths.csv, winequality-white.csv, winequality-red.csv</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Data Manipulation</t>
-  </si>
-  <si>
-    <t>Data Manipulation, Basic Concepts in Statistics</t>
-  </si>
-  <si>
-    <t>Model Validation, Supervised Learning, Data Manipulation</t>
-  </si>
-  <si>
-    <t>Supervised Learning,Regression</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Decision Tree, Model Validation</t>
-  </si>
-  <si>
-    <t>Consider a new wine with the following features, but unknown `type`. 
-```{python, echo=FALSE}
-wine2.sample(n=1, random_state=22).iloc[:, 0:11].T
-```
-Apply the decision tree rules to the above features to estimate the probability that the wine is *red*.</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Decision Trees, Model Validation, Basic Concepts in Statistics</t>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -454,13 +452,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -806,13 +800,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -820,10 +814,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -831,10 +825,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -858,87 +852,87 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>36</v>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="170" x14ac:dyDescent="0.2">
@@ -946,34 +940,34 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="238" x14ac:dyDescent="0.2">
@@ -981,31 +975,31 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>18</v>
       </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
       <c r="O4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1013,34 +1007,34 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="L5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
       <c r="O5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -1048,31 +1042,31 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>51</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>52</v>
       </c>
-      <c r="I6" t="s">
-        <v>53</v>
-      </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -1080,16 +1074,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>0.2</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7">
         <v>0.4</v>
@@ -1098,16 +1092,16 @@
         <v>0.6</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1115,34 +1109,34 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
         <v>58</v>
       </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>60</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>61</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="N8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -1153,10 +1147,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9">
         <v>0.995</v>
@@ -1171,16 +1165,16 @@
         <v>0.99</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -1191,10 +1185,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>8.0000000000000002E-3</v>
@@ -1209,16 +1203,16 @@
         <v>0.98399999999999999</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1229,22 +1223,22 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="K11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="N11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
